--- a/data/trans_orig/P36B08-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36B08-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de verduras, ensaladas y hortalizas en 2007</t>
+          <t>Población según la frecuencia de consumo de verduras, ensaladas y hortalizas en 2007 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6758</t>
+          <t>6655</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19980</t>
+          <t>20388</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>874</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7586</t>
+          <t>8477</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23867</t>
+          <t>23548</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16484</t>
+          <t>15302</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35198</t>
+          <t>34168</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16090</t>
+          <t>16196</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34674</t>
+          <t>34256</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>36560</t>
+          <t>36586</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>63189</t>
+          <t>62167</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>135294</t>
+          <t>133465</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>178456</t>
+          <t>177043</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>105979</t>
+          <t>105846</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>145485</t>
+          <t>146297</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>252822</t>
+          <t>252554</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>313729</t>
+          <t>309727</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,41%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>323870</t>
+          <t>327069</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>375878</t>
+          <t>377189</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>54,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>306112</t>
+          <t>304080</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>357142</t>
+          <t>354559</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>642422</t>
+          <t>643924</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>717565</t>
+          <t>718697</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>51,99%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>128601</t>
+          <t>130016</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>173269</t>
+          <t>171826</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>180013</t>
+          <t>182234</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>227764</t>
+          <t>230340</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>327131</t>
+          <t>328954</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>392637</t>
+          <t>391288</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,31%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10127</t>
+          <t>9246</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27313</t>
+          <t>27053</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9366</t>
+          <t>9086</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26445</t>
+          <t>26437</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22485</t>
+          <t>22795</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46812</t>
+          <t>47044</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>57566</t>
+          <t>57120</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>91741</t>
+          <t>93016</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29045</t>
+          <t>27977</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>54853</t>
+          <t>53820</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>92491</t>
+          <t>94656</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>136962</t>
+          <t>136655</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>245682</t>
+          <t>246360</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>302841</t>
+          <t>304770</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>219948</t>
+          <t>220333</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>274678</t>
+          <t>274517</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>478810</t>
+          <t>481710</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>557631</t>
+          <t>561024</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>29,08%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>361964</t>
+          <t>361435</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>420761</t>
+          <t>422011</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>368532</t>
+          <t>371534</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>432323</t>
+          <t>431904</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>44,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>746984</t>
+          <t>746474</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>840244</t>
+          <t>838907</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>43,49%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>181843</t>
+          <t>182716</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>234770</t>
+          <t>233068</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>236803</t>
+          <t>239061</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>294217</t>
+          <t>293821</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>433355</t>
+          <t>433067</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>512079</t>
+          <t>509146</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,39%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14908</t>
+          <t>14552</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35138</t>
+          <t>33988</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4785</t>
+          <t>4859</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16978</t>
+          <t>19406</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22145</t>
+          <t>22473</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45265</t>
+          <t>45610</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>41455</t>
+          <t>40005</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>69506</t>
+          <t>69116</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>25387</t>
+          <t>27177</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>50311</t>
+          <t>49455</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>72868</t>
+          <t>72245</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>109839</t>
+          <t>109135</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,01%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>184375</t>
+          <t>184598</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>233072</t>
+          <t>234141</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>135906</t>
+          <t>135635</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>177109</t>
+          <t>177625</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>331453</t>
+          <t>330487</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>396467</t>
+          <t>394320</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,94%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>224296</t>
+          <t>226405</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>276960</t>
+          <t>277903</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>253761</t>
+          <t>252846</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>305538</t>
+          <t>302634</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>494435</t>
+          <t>492531</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>567088</t>
+          <t>563530</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>41,36%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>120736</t>
+          <t>121668</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>163941</t>
+          <t>165675</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>182087</t>
+          <t>181480</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>230832</t>
+          <t>227553</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>315808</t>
+          <t>316171</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>377738</t>
+          <t>380619</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,94%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14107</t>
+          <t>14603</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31785</t>
+          <t>31150</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6928</t>
+          <t>6908</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20816</t>
+          <t>22006</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>25627</t>
+          <t>24322</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>48396</t>
+          <t>46471</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>62130</t>
+          <t>60915</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>95598</t>
+          <t>94717</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>34511</t>
+          <t>34147</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>61242</t>
+          <t>61431</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>103031</t>
+          <t>102721</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>147784</t>
+          <t>145434</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>239395</t>
+          <t>238651</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>290423</t>
+          <t>292273</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>233872</t>
+          <t>233780</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>288206</t>
+          <t>290570</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>487722</t>
+          <t>490670</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>566519</t>
+          <t>565421</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,56%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>360786</t>
+          <t>365678</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>418398</t>
+          <t>424709</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>418325</t>
+          <t>419483</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>480616</t>
+          <t>481524</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>801257</t>
+          <t>798818</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>889314</t>
+          <t>887918</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>44,84%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>162693</t>
+          <t>163936</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>209277</t>
+          <t>210687</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>240834</t>
+          <t>241799</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>295082</t>
+          <t>295355</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>417693</t>
+          <t>417073</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>489014</t>
+          <t>490866</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,79%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>57868</t>
+          <t>56905</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>90777</t>
+          <t>90075</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>29421</t>
+          <t>31621</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>56088</t>
+          <t>58176</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>95422</t>
+          <t>96065</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>137291</t>
+          <t>137659</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>200833</t>
+          <t>199044</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>258007</t>
+          <t>258577</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>123193</t>
+          <t>124038</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>170664</t>
+          <t>170982</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>340179</t>
+          <t>336777</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>413692</t>
+          <t>417686</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,28%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>854576</t>
+          <t>851550</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>955996</t>
+          <t>958089</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>744815</t>
+          <t>743328</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>839467</t>
+          <t>840486</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1622406</t>
+          <t>1621570</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1762318</t>
+          <t>1767594</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,56%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1330178</t>
+          <t>1328608</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1440369</t>
+          <t>1449638</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1408094</t>
+          <t>1401220</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1521099</t>
+          <t>1518811</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2769166</t>
+          <t>2757092</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2922925</t>
+          <t>2917282</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>43,84%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>639768</t>
+          <t>635779</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>736864</t>
+          <t>729273</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>889243</t>
+          <t>890788</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>996320</t>
+          <t>995068</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1552715</t>
+          <t>1552484</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1698620</t>
+          <t>1696921</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,5%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de verduras, ensaladas y hortalizas en 2012</t>
+          <t>Población según la frecuencia de consumo de verduras, ensaladas y hortalizas en 2012 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2744</t>
+          <t>2812</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13223</t>
+          <t>13023</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3073</t>
+          <t>3153</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14074</t>
+          <t>14700</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7844</t>
+          <t>8153</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22298</t>
+          <t>23774</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18171</t>
+          <t>18058</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38553</t>
+          <t>39565</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10058</t>
+          <t>10115</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27798</t>
+          <t>27059</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32257</t>
+          <t>33148</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>58767</t>
+          <t>60205</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>114469</t>
+          <t>117018</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>158938</t>
+          <t>160932</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>79252</t>
+          <t>79690</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>116847</t>
+          <t>117326</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>205793</t>
+          <t>206488</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>260394</t>
+          <t>264326</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,89%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>216323</t>
+          <t>215479</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>268731</t>
+          <t>269097</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>221492</t>
+          <t>223288</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>273739</t>
+          <t>274735</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>454715</t>
+          <t>456676</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>531236</t>
+          <t>527170</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>37,67%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>264572</t>
+          <t>263144</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>317850</t>
+          <t>316607</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>297959</t>
+          <t>302105</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>354360</t>
+          <t>354819</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>580210</t>
+          <t>578792</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>657742</t>
+          <t>655329</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>46,83%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9133</t>
+          <t>8253</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26606</t>
+          <t>25981</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3169</t>
+          <t>3240</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15450</t>
+          <t>16580</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14993</t>
+          <t>15471</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37713</t>
+          <t>36901</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38983</t>
+          <t>39265</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>68564</t>
+          <t>67745</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30074</t>
+          <t>29464</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>56099</t>
+          <t>57213</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>77712</t>
+          <t>76543</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>114472</t>
+          <t>117515</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>205480</t>
+          <t>199626</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>259994</t>
+          <t>256943</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>159057</t>
+          <t>158662</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>209367</t>
+          <t>211148</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>378164</t>
+          <t>374458</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>452927</t>
+          <t>451553</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,1%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>341412</t>
+          <t>338949</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>405573</t>
+          <t>402879</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>304756</t>
+          <t>303988</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>364870</t>
+          <t>365795</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>654584</t>
+          <t>665822</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>745253</t>
+          <t>751990</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,81%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>313270</t>
+          <t>312990</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>375665</t>
+          <t>378626</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>431544</t>
+          <t>426704</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>493424</t>
+          <t>497437</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>757520</t>
+          <t>763080</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>850072</t>
+          <t>857459</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>41,97%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11379</t>
+          <t>11466</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27699</t>
+          <t>26868</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4987</t>
+          <t>4963</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17668</t>
+          <t>16938</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19516</t>
+          <t>19787</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39760</t>
+          <t>40624</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22490</t>
+          <t>21942</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>44663</t>
+          <t>44304</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11099</t>
+          <t>10979</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28351</t>
+          <t>30141</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37397</t>
+          <t>37714</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>66113</t>
+          <t>67059</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>180148</t>
+          <t>179042</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>232035</t>
+          <t>232204</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>145852</t>
+          <t>142978</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>193659</t>
+          <t>191536</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>341696</t>
+          <t>337934</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>411205</t>
+          <t>411023</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,84%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>264219</t>
+          <t>264151</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>323820</t>
+          <t>320708</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>285149</t>
+          <t>286626</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>341065</t>
+          <t>345184</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>565407</t>
+          <t>566383</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>644327</t>
+          <t>646632</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>42,07%</t>
+          <t>42,22%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>180227</t>
+          <t>182318</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>234347</t>
+          <t>233736</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>239117</t>
+          <t>238893</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>294749</t>
+          <t>291993</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>432018</t>
+          <t>436832</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>509093</t>
+          <t>513563</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,53%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9305</t>
+          <t>9148</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>25882</t>
+          <t>25732</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5953</t>
+          <t>6018</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19207</t>
+          <t>19944</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17547</t>
+          <t>17520</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>38518</t>
+          <t>39204</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6510,7 +6510,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>26750</t>
+          <t>26256</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>51010</t>
+          <t>49176</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>18342</t>
+          <t>17815</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>40645</t>
+          <t>38285</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>49499</t>
+          <t>49838</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>81172</t>
+          <t>79771</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>184026</t>
+          <t>185765</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>235549</t>
+          <t>237147</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>114556</t>
+          <t>113707</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>157540</t>
+          <t>156979</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>311626</t>
+          <t>313991</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>379850</t>
+          <t>382726</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,19%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>269980</t>
+          <t>271297</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>328343</t>
+          <t>331462</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>261501</t>
+          <t>261053</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>319459</t>
+          <t>319196</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>548295</t>
+          <t>548829</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>631444</t>
+          <t>630974</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,64%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>352780</t>
+          <t>355843</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>417084</t>
+          <t>419233</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>44,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>550154</t>
+          <t>551086</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>615689</t>
+          <t>615455</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>58,85%</t>
+          <t>58,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>928265</t>
+          <t>923632</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1017475</t>
+          <t>1016795</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>50,99%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>43028</t>
+          <t>42700</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>73727</t>
+          <t>73657</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>25750</t>
+          <t>25962</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>49537</t>
+          <t>50022</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>74979</t>
+          <t>74871</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>113070</t>
+          <t>112609</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,7 +7187,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>124031</t>
+          <t>126884</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>173909</t>
+          <t>175503</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>85076</t>
+          <t>85146</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>125424</t>
+          <t>126348</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7270,7 +7270,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>221996</t>
+          <t>221998</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>287459</t>
+          <t>287915</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>730396</t>
+          <t>734509</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>837399</t>
+          <t>833705</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>544265</t>
+          <t>543194</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>635117</t>
+          <t>633950</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1298980</t>
+          <t>1290831</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1429628</t>
+          <t>1436488</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,62%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1145614</t>
+          <t>1141500</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1260947</t>
+          <t>1263377</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1121950</t>
+          <t>1132557</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1239060</t>
+          <t>1242278</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2307767</t>
+          <t>2308994</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2473437</t>
+          <t>2469983</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,45%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1173373</t>
+          <t>1172466</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1295687</t>
+          <t>1286083</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1576366</t>
+          <t>1576068</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1704181</t>
+          <t>1698483</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2777249</t>
+          <t>2790129</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2954415</t>
+          <t>2958640</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,46%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de verduras, ensaladas y hortalizas en 2016</t>
+          <t>Población según la frecuencia de consumo de verduras, ensaladas y hortalizas en 2016 (tasa de respuesta: 99,53%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2980</t>
+          <t>3060</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13828</t>
+          <t>14910</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,82 +8031,82 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>2,22%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>9706</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>4885</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>19769</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2,95%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>16548</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>9674</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>27669</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
           <t>2,06%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>9706</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>4552</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>18755</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,8%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>16548</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>9455</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>26375</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17366</t>
+          <t>16679</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38182</t>
+          <t>37589</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10491</t>
+          <t>10055</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28148</t>
+          <t>27771</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31249</t>
+          <t>31534</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>58153</t>
+          <t>56442</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>120115</t>
+          <t>121084</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>163622</t>
+          <t>164421</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>113437</t>
+          <t>114755</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>155475</t>
+          <t>155495</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,7 +8292,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>245864</t>
+          <t>245475</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>306561</t>
+          <t>309252</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>23,07%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>252931</t>
+          <t>253642</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>306565</t>
+          <t>305256</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>220032</t>
+          <t>221793</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>268988</t>
+          <t>270445</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>487431</t>
+          <t>488897</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>561810</t>
+          <t>558876</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>41,69%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>193597</t>
+          <t>194888</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>244921</t>
+          <t>240913</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>236883</t>
+          <t>237470</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>288967</t>
+          <t>287179</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>446518</t>
+          <t>445509</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>516185</t>
+          <t>515288</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,44%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5492</t>
+          <t>5512</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18920</t>
+          <t>17803</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9736</t>
+          <t>10159</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27572</t>
+          <t>27649</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,7 +8748,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17170</t>
+          <t>17291</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37719</t>
+          <t>39090</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32139</t>
+          <t>33172</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>58760</t>
+          <t>60620</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18534</t>
+          <t>17838</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40024</t>
+          <t>38110</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>56411</t>
+          <t>55932</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>90277</t>
+          <t>89140</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>205936</t>
+          <t>205307</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>261289</t>
+          <t>259925</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>174055</t>
+          <t>175384</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>225997</t>
+          <t>228807</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>385741</t>
+          <t>395676</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>467728</t>
+          <t>471263</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,84%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>458194</t>
+          <t>457352</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>520950</t>
+          <t>522689</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>44,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>461374</t>
+          <t>458350</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>524802</t>
+          <t>526882</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>932771</t>
+          <t>937878</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1028341</t>
+          <t>1027967</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>49,82%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>218823</t>
+          <t>217592</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>274427</t>
+          <t>272621</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,47 +9165,47 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>26,69%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>306646</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>279913</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>339854</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>29,43%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
           <t>26,87%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>306646</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>277162</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>339069</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>29,43%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>26,6%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>509173</t>
+          <t>512436</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>590411</t>
+          <t>595009</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,84%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4140</t>
+          <t>4108</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15949</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9400,7 +9400,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3234</t>
+          <t>3971</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14883</t>
+          <t>15297</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9183</t>
+          <t>10221</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25816</t>
+          <t>26559</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28785</t>
+          <t>28332</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>54267</t>
+          <t>53855</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14365</t>
+          <t>13797</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33434</t>
+          <t>33411</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>47097</t>
+          <t>47132</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>81025</t>
+          <t>82195</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>175570</t>
+          <t>178462</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>227142</t>
+          <t>228568</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>154996</t>
+          <t>156990</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>202885</t>
+          <t>204282</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>345073</t>
+          <t>347426</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>414010</t>
+          <t>418494</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,39%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>294668</t>
+          <t>292998</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>349478</t>
+          <t>350315</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>289937</t>
+          <t>288343</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>343946</t>
+          <t>345781</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,47 +9769,47 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
+          <t>44,41%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>638623</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>593525</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>675013</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>41,8%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>38,85%</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
           <t>44,18%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>593</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>638623</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>600813</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>679321</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>41,8%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>39,32%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>44,46%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>154940</t>
+          <t>155813</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>201000</t>
+          <t>201520</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>225112</t>
+          <t>227006</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>280073</t>
+          <t>278684</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>394774</t>
+          <t>395505</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>466920</t>
+          <t>473168</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,97%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6847</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20686</t>
+          <t>20914</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4090</t>
+          <t>3953</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17431</t>
+          <t>16196</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,47 +10112,47 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>21256</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>13683</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>33078</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
           <t>1,68%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>21256</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>13235</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>32028</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>19867</t>
+          <t>20781</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>43550</t>
+          <t>42759</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>15964</t>
+          <t>15729</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>35527</t>
+          <t>36224</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>42182</t>
+          <t>40619</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>71213</t>
+          <t>70248</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>159721</t>
+          <t>160343</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>206498</t>
+          <t>207848</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>126229</t>
+          <t>127118</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>171509</t>
+          <t>173447</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>297760</t>
+          <t>295276</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>363129</t>
+          <t>362937</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,39%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>386347</t>
+          <t>387851</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>448397</t>
+          <t>445714</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>397248</t>
+          <t>397480</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>465437</t>
+          <t>460559</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>44,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>804308</t>
+          <t>802625</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>893061</t>
+          <t>890749</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>45,14%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>266139</t>
+          <t>267488</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>321929</t>
+          <t>322783</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>395577</t>
+          <t>395198</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>459115</t>
+          <t>457739</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>675673</t>
+          <t>674337</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>764839</t>
+          <t>764017</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>38,72%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>27801</t>
+          <t>27509</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>53699</t>
+          <t>53338</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>30361</t>
+          <t>32696</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>57846</t>
+          <t>60270</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>64723</t>
+          <t>66372</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>100359</t>
+          <t>100317</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,7 +10829,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>117848</t>
+          <t>116110</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>166551</t>
+          <t>162646</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>73623</t>
+          <t>72987</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>111942</t>
+          <t>110329</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>203217</t>
+          <t>202747</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>265688</t>
+          <t>263161</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10947,7 +10947,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>707009</t>
+          <t>708403</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>806580</t>
+          <t>805500</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>615554</t>
+          <t>617372</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>712879</t>
+          <t>707117</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1342270</t>
+          <t>1349988</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1489315</t>
+          <t>1489577</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,7 +11055,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1441472</t>
+          <t>1450212</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1561068</t>
+          <t>1564718</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1424203</t>
+          <t>1426101</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1548965</t>
+          <t>1543031</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2907726</t>
+          <t>2903578</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3073302</t>
+          <t>3071431</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>44,48%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>881498</t>
+          <t>884006</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>988985</t>
+          <t>989339</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1186791</t>
+          <t>1192083</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1309476</t>
+          <t>1309739</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2104957</t>
+          <t>2099827</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2261453</t>
+          <t>2266412</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,82%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36B08-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36B08-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6655</t>
+          <t>6758</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20388</t>
+          <t>19745</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>881</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8477</t>
+          <t>7549</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8820</t>
+          <t>8549</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23548</t>
+          <t>23812</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15302</t>
+          <t>16167</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34168</t>
+          <t>35011</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16196</t>
+          <t>16582</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34256</t>
+          <t>34120</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>36586</t>
+          <t>36498</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>62167</t>
+          <t>63286</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>133465</t>
+          <t>133790</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>177043</t>
+          <t>180703</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>105846</t>
+          <t>106245</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>146297</t>
+          <t>146101</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>252554</t>
+          <t>253091</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>309727</t>
+          <t>311446</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,53%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>327069</t>
+          <t>325252</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>377189</t>
+          <t>377388</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>46,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>54,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>304080</t>
+          <t>303754</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>354559</t>
+          <t>354885</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>643924</t>
+          <t>643288</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>718697</t>
+          <t>713148</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>46,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>51,59%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>130016</t>
+          <t>130113</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>171826</t>
+          <t>174892</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>182234</t>
+          <t>183578</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>230340</t>
+          <t>229069</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>328954</t>
+          <t>325348</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>391288</t>
+          <t>386163</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>27,94%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9246</t>
+          <t>9378</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27053</t>
+          <t>27364</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,49 +1429,49 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>2,85%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>16219</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>10038</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>27224</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
           <t>2,81%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>16219</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>9086</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>26437</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>30</t>
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22795</t>
+          <t>22282</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>47044</t>
+          <t>46364</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>57120</t>
+          <t>57837</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>93016</t>
+          <t>92953</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27977</t>
+          <t>28947</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>53820</t>
+          <t>53954</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>94656</t>
+          <t>90688</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>136655</t>
+          <t>135483</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,02%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>246360</t>
+          <t>247119</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>304770</t>
+          <t>303944</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>220333</t>
+          <t>218047</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>274517</t>
+          <t>274923</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>481710</t>
+          <t>483173</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>561024</t>
+          <t>560698</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,06%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>361435</t>
+          <t>362334</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>422011</t>
+          <t>424230</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>371534</t>
+          <t>366457</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>431904</t>
+          <t>430458</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>746474</t>
+          <t>749999</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>838907</t>
+          <t>839326</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,51%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>182716</t>
+          <t>182394</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>233068</t>
+          <t>234394</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>239061</t>
+          <t>234531</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>293821</t>
+          <t>293543</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>433067</t>
+          <t>434333</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>509146</t>
+          <t>511855</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,53%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14552</t>
+          <t>14403</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33988</t>
+          <t>33394</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4859</t>
+          <t>4865</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19406</t>
+          <t>18026</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22473</t>
+          <t>22351</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45610</t>
+          <t>45010</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>40005</t>
+          <t>40755</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>69116</t>
+          <t>68691</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27177</t>
+          <t>26025</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>49455</t>
+          <t>50641</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>72245</t>
+          <t>73224</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>109135</t>
+          <t>108593</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>184598</t>
+          <t>186075</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>234141</t>
+          <t>235483</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>135635</t>
+          <t>132245</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>177625</t>
+          <t>174742</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>330487</t>
+          <t>329122</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>394320</t>
+          <t>393318</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,87%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>226405</t>
+          <t>224972</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>277903</t>
+          <t>279842</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>252846</t>
+          <t>255192</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>302634</t>
+          <t>304566</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>44,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>492531</t>
+          <t>492402</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>563530</t>
+          <t>565468</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>41,51%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>121668</t>
+          <t>120372</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>165675</t>
+          <t>165499</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>181480</t>
+          <t>178918</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>227553</t>
+          <t>228364</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>316171</t>
+          <t>313965</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>380619</t>
+          <t>379075</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>27,83%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14603</t>
+          <t>14844</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31150</t>
+          <t>32673</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6908</t>
+          <t>7112</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22006</t>
+          <t>22137</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>24322</t>
+          <t>25436</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>46471</t>
+          <t>47183</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>60915</t>
+          <t>61215</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>94717</t>
+          <t>94833</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>34147</t>
+          <t>33555</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>61431</t>
+          <t>62181</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>102721</t>
+          <t>102369</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>145434</t>
+          <t>145420</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>238651</t>
+          <t>240137</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>292273</t>
+          <t>293446</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>233780</t>
+          <t>235022</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>290570</t>
+          <t>291749</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>490670</t>
+          <t>486420</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>565421</t>
+          <t>566669</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,62%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>365678</t>
+          <t>361176</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>424709</t>
+          <t>421521</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>44,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>419483</t>
+          <t>416000</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>481524</t>
+          <t>480134</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>798818</t>
+          <t>800482</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>887918</t>
+          <t>887197</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>44,81%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>163936</t>
+          <t>165047</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>210687</t>
+          <t>213023</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>241799</t>
+          <t>239612</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>295355</t>
+          <t>295044</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>417073</t>
+          <t>418170</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>490866</t>
+          <t>489557</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,73%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>56905</t>
+          <t>58615</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>90075</t>
+          <t>93187</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>31621</t>
+          <t>30571</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>58176</t>
+          <t>54747</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,47 +3510,47 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>114452</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>93390</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>136831</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
           <t>1,72%</t>
         </is>
       </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>114452</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>96065</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>137659</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>199044</t>
+          <t>198201</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>258577</t>
+          <t>259674</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>124038</t>
+          <t>124714</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>170982</t>
+          <t>172489</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>336777</t>
+          <t>334398</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>417686</t>
+          <t>412505</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>851550</t>
+          <t>849640</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>958089</t>
+          <t>952507</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>743328</t>
+          <t>739890</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>840486</t>
+          <t>836129</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1621570</t>
+          <t>1625428</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1767594</t>
+          <t>1768899</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,58%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1328608</t>
+          <t>1330399</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1449638</t>
+          <t>1440650</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>43,98%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1401220</t>
+          <t>1405585</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1518811</t>
+          <t>1515839</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2757092</t>
+          <t>2770306</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2917282</t>
+          <t>2927119</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>43,99%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>635779</t>
+          <t>640610</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>729273</t>
+          <t>731622</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>890788</t>
+          <t>887831</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>995068</t>
+          <t>990314</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1552484</t>
+          <t>1562661</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1696921</t>
+          <t>1698029</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,52%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2812</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13023</t>
+          <t>13719</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3153</t>
+          <t>3116</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14700</t>
+          <t>14717</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8153</t>
+          <t>8074</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23774</t>
+          <t>22918</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18058</t>
+          <t>17164</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39565</t>
+          <t>39112</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10115</t>
+          <t>10174</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27059</t>
+          <t>27107</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33148</t>
+          <t>32047</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>60205</t>
+          <t>57892</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>117018</t>
+          <t>116459</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>160932</t>
+          <t>157654</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>79690</t>
+          <t>78664</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>117326</t>
+          <t>116498</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>206488</t>
+          <t>203882</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>264326</t>
+          <t>261423</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,68%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>215479</t>
+          <t>215484</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>269097</t>
+          <t>266456</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>223288</t>
+          <t>224996</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>274735</t>
+          <t>274104</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>456676</t>
+          <t>455260</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>527170</t>
+          <t>525538</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>37,55%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>263144</t>
+          <t>263026</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>316607</t>
+          <t>317594</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>302105</t>
+          <t>302178</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>354819</t>
+          <t>355925</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>51,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>578792</t>
+          <t>582032</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>655329</t>
+          <t>656426</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>46,91%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8253</t>
+          <t>8813</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25981</t>
+          <t>27203</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3240</t>
+          <t>3493</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16580</t>
+          <t>17874</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15471</t>
+          <t>15319</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36901</t>
+          <t>36773</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39265</t>
+          <t>40467</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>67745</t>
+          <t>69448</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29464</t>
+          <t>29240</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>57213</t>
+          <t>56037</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>76543</t>
+          <t>74989</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>117515</t>
+          <t>115070</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>199626</t>
+          <t>203131</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>256943</t>
+          <t>257063</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>158662</t>
+          <t>159094</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>211148</t>
+          <t>210416</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>374458</t>
+          <t>377494</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>451553</t>
+          <t>453774</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,21%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>338949</t>
+          <t>339867</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>402879</t>
+          <t>405748</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>303988</t>
+          <t>303275</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>365795</t>
+          <t>365483</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>665822</t>
+          <t>664618</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>751990</t>
+          <t>751956</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>312990</t>
+          <t>312256</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>378626</t>
+          <t>376743</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>426704</t>
+          <t>427264</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>497437</t>
+          <t>493484</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>763080</t>
+          <t>767140</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>857459</t>
+          <t>858385</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>42,02%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11466</t>
+          <t>11595</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26868</t>
+          <t>28639</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4963</t>
+          <t>4935</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16938</t>
+          <t>17746</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19787</t>
+          <t>19310</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>40624</t>
+          <t>39922</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21942</t>
+          <t>21399</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>44304</t>
+          <t>44924</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10979</t>
+          <t>10858</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30141</t>
+          <t>29245</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37714</t>
+          <t>38087</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>67059</t>
+          <t>66723</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>179042</t>
+          <t>180686</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>232204</t>
+          <t>233174</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>142978</t>
+          <t>145726</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>191536</t>
+          <t>193227</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>337934</t>
+          <t>338563</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>411023</t>
+          <t>412676</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,94%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>264151</t>
+          <t>263612</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>320708</t>
+          <t>322470</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>286626</t>
+          <t>282564</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>345184</t>
+          <t>342125</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>566383</t>
+          <t>566805</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>646632</t>
+          <t>647456</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>42,27%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>182318</t>
+          <t>180523</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>233736</t>
+          <t>233185</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>238893</t>
+          <t>240373</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>291993</t>
+          <t>295684</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>436832</t>
+          <t>437013</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>513563</t>
+          <t>514317</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,58%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9148</t>
+          <t>8622</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>25732</t>
+          <t>25582</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6018</t>
+          <t>5857</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19944</t>
+          <t>18760</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17520</t>
+          <t>17210</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>39204</t>
+          <t>39075</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>26256</t>
+          <t>26710</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>49176</t>
+          <t>49491</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>17815</t>
+          <t>18476</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>38285</t>
+          <t>40508</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>49838</t>
+          <t>48682</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>79771</t>
+          <t>80822</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>185765</t>
+          <t>183951</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>237147</t>
+          <t>235243</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>113707</t>
+          <t>113995</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>156979</t>
+          <t>159025</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>313991</t>
+          <t>309982</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>382726</t>
+          <t>382697</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>271297</t>
+          <t>268081</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>331462</t>
+          <t>326255</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>261053</t>
+          <t>263794</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>319196</t>
+          <t>323196</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>548829</t>
+          <t>548920</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>630974</t>
+          <t>634593</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,83%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>355843</t>
+          <t>356528</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>419233</t>
+          <t>417110</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>551086</t>
+          <t>548033</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>615455</t>
+          <t>610796</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>58,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>923632</t>
+          <t>918527</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1016795</t>
+          <t>1010916</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>50,7%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>42700</t>
+          <t>41988</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>73657</t>
+          <t>71533</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>25962</t>
+          <t>24988</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>50022</t>
+          <t>49735</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>74871</t>
+          <t>74482</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>112609</t>
+          <t>113072</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>126884</t>
+          <t>127052</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>175503</t>
+          <t>173616</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>85146</t>
+          <t>85449</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>126348</t>
+          <t>127618</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>221998</t>
+          <t>223297</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>287915</t>
+          <t>290029</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>734509</t>
+          <t>734422</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>833705</t>
+          <t>835277</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>543194</t>
+          <t>540566</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>633950</t>
+          <t>635144</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1290831</t>
+          <t>1299128</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1436488</t>
+          <t>1432622</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,56%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1141500</t>
+          <t>1142447</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1263377</t>
+          <t>1260521</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1132557</t>
+          <t>1124073</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1242278</t>
+          <t>1242896</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2308994</t>
+          <t>2314189</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2469983</t>
+          <t>2475009</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,52%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1172466</t>
+          <t>1170036</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1286083</t>
+          <t>1285828</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1576068</t>
+          <t>1579634</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1698483</t>
+          <t>1706191</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>48,08%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2790129</t>
+          <t>2774961</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2958640</t>
+          <t>2947365</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>42,3%</t>
         </is>
       </c>
     </row>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3060</t>
+          <t>2861</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14910</t>
+          <t>14299</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4885</t>
+          <t>4952</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19769</t>
+          <t>18732</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9674</t>
+          <t>10074</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27669</t>
+          <t>27375</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16679</t>
+          <t>16804</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37589</t>
+          <t>37347</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10055</t>
+          <t>10446</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27771</t>
+          <t>28317</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31534</t>
+          <t>32421</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>56442</t>
+          <t>57032</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>121084</t>
+          <t>121367</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>164421</t>
+          <t>162667</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>114755</t>
+          <t>117169</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>155495</t>
+          <t>156448</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>245475</t>
+          <t>249226</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>309252</t>
+          <t>308025</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,98%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>253642</t>
+          <t>254119</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>305256</t>
+          <t>305789</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>221793</t>
+          <t>219013</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>270445</t>
+          <t>267302</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>488897</t>
+          <t>485431</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>558876</t>
+          <t>555647</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>41,45%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>194888</t>
+          <t>194911</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>240913</t>
+          <t>243090</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8488,7 +8488,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>237470</t>
+          <t>236611</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>287179</t>
+          <t>287947</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>445509</t>
+          <t>446875</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>515288</t>
+          <t>516281</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,51%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5512</t>
+          <t>5072</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17803</t>
+          <t>18346</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10159</t>
+          <t>10044</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27649</t>
+          <t>26486</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17291</t>
+          <t>18030</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39090</t>
+          <t>39808</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33172</t>
+          <t>32488</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>60620</t>
+          <t>59192</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17838</t>
+          <t>18322</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38110</t>
+          <t>38632</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>55932</t>
+          <t>56126</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>89140</t>
+          <t>92567</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>205307</t>
+          <t>205439</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>259925</t>
+          <t>258053</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>175384</t>
+          <t>174118</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>228807</t>
+          <t>226656</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>395676</t>
+          <t>396349</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>471263</t>
+          <t>469891</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,78%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>457352</t>
+          <t>459558</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>522689</t>
+          <t>524420</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>458350</t>
+          <t>456888</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>526882</t>
+          <t>525744</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>50,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>937878</t>
+          <t>935316</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1027967</t>
+          <t>1027879</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>217592</t>
+          <t>216412</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>272621</t>
+          <t>274105</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>279913</t>
+          <t>277415</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>339854</t>
+          <t>339368</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>512436</t>
+          <t>509318</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>595009</t>
+          <t>595176</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,85%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4108</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16312</t>
+          <t>16573</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3971</t>
+          <t>3894</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15297</t>
+          <t>15857</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10221</t>
+          <t>9530</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26559</t>
+          <t>26098</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28332</t>
+          <t>28219</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>53855</t>
+          <t>54505</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13797</t>
+          <t>13429</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33411</t>
+          <t>33330</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>47132</t>
+          <t>47455</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>82195</t>
+          <t>81116</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178462</t>
+          <t>176229</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>228568</t>
+          <t>228455</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>156990</t>
+          <t>155687</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>204282</t>
+          <t>203219</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>347426</t>
+          <t>347205</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>418494</t>
+          <t>413570</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,07%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>292998</t>
+          <t>291470</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>350315</t>
+          <t>350143</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>288343</t>
+          <t>290092</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>345781</t>
+          <t>347200</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>593525</t>
+          <t>598060</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>675013</t>
+          <t>674079</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>44,12%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>155813</t>
+          <t>153520</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>201520</t>
+          <t>200473</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>227006</t>
+          <t>225085</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>278684</t>
+          <t>279403</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>395505</t>
+          <t>398411</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>473168</t>
+          <t>473703</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>31,0%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>6874</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20914</t>
+          <t>21413</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3953</t>
+          <t>3866</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16196</t>
+          <t>16465</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13683</t>
+          <t>13316</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>33078</t>
+          <t>31442</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>20781</t>
+          <t>20356</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>42759</t>
+          <t>41758</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>15729</t>
+          <t>16473</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>36224</t>
+          <t>36320</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>40619</t>
+          <t>39692</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>70248</t>
+          <t>70012</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>160343</t>
+          <t>159638</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>207848</t>
+          <t>209232</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>127118</t>
+          <t>125994</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>173447</t>
+          <t>170415</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>295276</t>
+          <t>300238</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>362937</t>
+          <t>364250</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,46%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>387851</t>
+          <t>386233</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>445714</t>
+          <t>445095</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>47,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>397480</t>
+          <t>399068</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>460559</t>
+          <t>464064</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>44,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>802625</t>
+          <t>797969</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>890749</t>
+          <t>887678</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>44,99%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>267488</t>
+          <t>268228</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>322783</t>
+          <t>326753</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>395198</t>
+          <t>397604</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>457739</t>
+          <t>461188</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>44,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>674337</t>
+          <t>682244</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>764017</t>
+          <t>766458</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>38,84%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>27509</t>
+          <t>27877</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>53338</t>
+          <t>52448</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>32696</t>
+          <t>32304</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>60270</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>66372</t>
+          <t>64815</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>100317</t>
+          <t>100761</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>116110</t>
+          <t>116335</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>162646</t>
+          <t>163648</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10877,7 +10877,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>72987</t>
+          <t>73371</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>110329</t>
+          <t>112517</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>202747</t>
+          <t>201852</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>263161</t>
+          <t>263466</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>708403</t>
+          <t>700759</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>805500</t>
+          <t>804285</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>617372</t>
+          <t>620633</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>707117</t>
+          <t>713365</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1349988</t>
+          <t>1351979</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1489577</t>
+          <t>1491043</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,59%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1450212</t>
+          <t>1447110</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1564718</t>
+          <t>1564927</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1426101</t>
+          <t>1424906</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1543031</t>
+          <t>1547142</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2903578</t>
+          <t>2903697</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3071431</t>
+          <t>3076770</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11173,7 +11173,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>44,56%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>884006</t>
+          <t>887873</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>989339</t>
+          <t>987545</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1192083</t>
+          <t>1188779</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1309739</t>
+          <t>1305563</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2099827</t>
+          <t>2107289</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2266412</t>
+          <t>2262397</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,76%</t>
         </is>
       </c>
     </row>
